--- a/docs/downloads/20260827_Seputeh Hills_Teduh Weekly Update.xlsx
+++ b/docs/downloads/20260827_Seputeh Hills_Teduh Weekly Update.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,10 @@
     <col width="9" customWidth="1" min="22" max="22"/>
     <col width="9" customWidth="1" min="23" max="23"/>
     <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="42" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
+    <col width="42" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,8 +552,11 @@
       <c r="S3" s="3" t="n">
         <v>46248</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="V3" s="3" t="n">
         <v>46255</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>46262</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -661,22 +667,37 @@
           <t>%</t>
         </is>
       </c>
-      <c r="V4" s="6" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="W4" s="6" t="inlineStr">
+      <c r="W4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="X4" s="6" t="inlineStr">
+      <c r="X4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="Y4" s="5" t="inlineStr">
+      <c r="Y4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="Z4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AA4" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AB4" s="5" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -761,18 +782,29 @@
         <f>T5/$F$5</f>
         <v/>
       </c>
-      <c r="V5" s="12">
+      <c r="V5" s="10">
         <f>W5-T5</f>
         <v/>
       </c>
-      <c r="W5" s="12" t="n">
+      <c r="W5" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="X5" s="13">
+      <c r="X5" s="11">
         <f>W5/$F$5</f>
         <v/>
       </c>
-      <c r="Y5" s="8" t="inlineStr">
+      <c r="Y5" s="12">
+        <f>Z5-W5</f>
+        <v/>
+      </c>
+      <c r="Z5" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA5" s="13">
+        <f>Z5/$F$5</f>
+        <v/>
+      </c>
+      <c r="AB5" s="8" t="inlineStr">
         <is>
           <t>Big unit (5,533 to Penthouse 19,031sqft)</t>
         </is>
@@ -857,18 +889,29 @@
         <f>T6/$F$6</f>
         <v/>
       </c>
-      <c r="V6" s="12">
+      <c r="V6" s="10">
         <f>W6-T6</f>
         <v/>
       </c>
-      <c r="W6" s="12" t="n">
+      <c r="W6" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="X6" s="13">
+      <c r="X6" s="11">
         <f>W6/$F$6</f>
         <v/>
       </c>
-      <c r="Y6" s="8" t="inlineStr">
+      <c r="Y6" s="12">
+        <f>Z6-W6</f>
+        <v/>
+      </c>
+      <c r="Z6" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA6" s="13">
+        <f>Z6/$F$6</f>
+        <v/>
+      </c>
+      <c r="AB6" s="8" t="inlineStr">
         <is>
           <t>Big unit (3,380 to 4,090sqft  &amp; Penthouse 7,459sqft).</t>
         </is>
@@ -953,18 +996,29 @@
         <f>T7/$F$7</f>
         <v/>
       </c>
-      <c r="V7" s="12">
+      <c r="V7" s="10">
         <f>W7-T7</f>
         <v/>
       </c>
-      <c r="W7" s="12" t="n">
+      <c r="W7" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="X7" s="13">
+      <c r="X7" s="11">
         <f>W7/$F$7</f>
         <v/>
       </c>
-      <c r="Y7" s="8" t="inlineStr">
+      <c r="Y7" s="12">
+        <f>Z7-W7</f>
+        <v/>
+      </c>
+      <c r="Z7" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA7" s="13">
+        <f>Z7/$F$7</f>
+        <v/>
+      </c>
+      <c r="AB7" s="8" t="inlineStr">
         <is>
           <t>Small unit (452 to 1,679 sq ft)</t>
         </is>
@@ -1049,18 +1103,29 @@
         <f>T8/$F$8</f>
         <v/>
       </c>
-      <c r="V8" s="12">
+      <c r="V8" s="10">
         <f>W8-T8</f>
         <v/>
       </c>
-      <c r="W8" s="12" t="n">
+      <c r="W8" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="X8" s="13">
+      <c r="X8" s="11">
         <f>W8/$F$8</f>
         <v/>
       </c>
-      <c r="Y8" s="8" t="inlineStr">
+      <c r="Y8" s="12">
+        <f>Z8-W8</f>
+        <v/>
+      </c>
+      <c r="Z8" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA8" s="13">
+        <f>Z8/$F$8</f>
+        <v/>
+      </c>
+      <c r="AB8" s="8" t="inlineStr">
         <is>
           <t>4-storey Villa (4,854 to 5,157 sq ft); left 3 bumi units</t>
         </is>
@@ -1145,18 +1210,29 @@
         <f>T9/$F$9</f>
         <v/>
       </c>
-      <c r="V9" s="12">
+      <c r="V9" s="10">
         <f>W9-T9</f>
         <v/>
       </c>
-      <c r="W9" s="12" t="n">
+      <c r="W9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="X9" s="13">
+      <c r="X9" s="11">
         <f>W9/$F$9</f>
         <v/>
       </c>
-      <c r="Y9" s="8" t="inlineStr">
+      <c r="Y9" s="12">
+        <f>Z9-W9</f>
+        <v/>
+      </c>
+      <c r="Z9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="13">
+        <f>Z9/$F$9</f>
+        <v/>
+      </c>
+      <c r="AB9" s="8" t="inlineStr">
         <is>
           <t>Big unit (1,648 to 3,856 sq ft)</t>
         </is>
@@ -1231,18 +1307,29 @@
         <f>T10/$F$10</f>
         <v/>
       </c>
-      <c r="V10" s="12">
+      <c r="V10" s="10">
         <f>W10-T10</f>
         <v/>
       </c>
-      <c r="W10" s="12" t="n">
+      <c r="W10" s="10" t="n">
         <v>335</v>
       </c>
-      <c r="X10" s="13">
+      <c r="X10" s="11">
         <f>W10/$F$10</f>
         <v/>
       </c>
-      <c r="Y10" s="8" t="inlineStr">
+      <c r="Y10" s="12">
+        <f>Z10-W10</f>
+        <v/>
+      </c>
+      <c r="Z10" s="12" t="n">
+        <v>346</v>
+      </c>
+      <c r="AA10" s="13">
+        <f>Z10/$F$10</f>
+        <v/>
+      </c>
+      <c r="AB10" s="8" t="inlineStr">
         <is>
           <t>Big unit (2,842 to 10,613 sq ft)</t>
         </is>
@@ -1286,22 +1373,34 @@
       <c r="S11" s="10" t="n"/>
       <c r="T11" s="10" t="n"/>
       <c r="U11" s="11" t="n"/>
-      <c r="V11" s="12" t="n"/>
-      <c r="W11" s="12" t="n">
+      <c r="V11" s="10" t="n"/>
+      <c r="W11" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="X11" s="13">
+      <c r="X11" s="11">
         <f>W11/$F$11</f>
         <v/>
       </c>
-      <c r="Y11" s="8" t="inlineStr">
+      <c r="Y11" s="12">
+        <f>Z11-W11</f>
+        <v/>
+      </c>
+      <c r="Z11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="13">
+        <f>Z11/$F$11</f>
+        <v/>
+      </c>
+      <c r="AB11" s="8" t="inlineStr">
         <is>
           <t>Not yet launched</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="Y3:AA3"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="G3:I3"/>
